--- a/banks/W16_Kahoot匯入.xlsx
+++ b/banks/W16_Kahoot匯入.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -491,30 +491,30 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>尿素循環</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>肉鹼穿梭</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>β-氧化</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>脂解作用</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>β-氧化</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>尿素循環</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>肉鹼穿梭</t>
-        </is>
-      </c>
       <c r="F2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -531,25 +531,25 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>去胺作用</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
           <t>肉鹼穿梭</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>脂解作用</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>去胺作用</t>
-        </is>
-      </c>
       <c r="F3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -561,17 +561,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>去胺作用</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>肉鹼穿梭</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>麩胺酸</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>肉鹼穿梭</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>去胺作用</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -596,30 +596,30 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>脂解作用</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>β-氧化</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>脂解作用</t>
-        </is>
-      </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>醯基輔酶A</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>生糖胺基酸</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>醯基輔酶A</t>
-        </is>
-      </c>
       <c r="F5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -631,14 +631,14 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>酮體</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>尿素</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>酮體</t>
-        </is>
-      </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>銨離子</t>
@@ -654,7 +654,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -666,19 +666,19 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>轉胺作用</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>去胺作用</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>生酮作用</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>去胺作用</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>轉胺作用</t>
-        </is>
-      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
           <t>尿素循環</t>
@@ -689,7 +689,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -706,25 +706,25 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>尿素循環</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>去胺作用</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>轉胺作用</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>尿素循環</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -741,25 +741,25 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>麩胺酸</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>轉胺酶</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>脂解作用</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>麩胺酸</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>轉胺酶</t>
-        </is>
-      </c>
       <c r="F9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -771,30 +771,30 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>生糖胺基酸</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>β-氧化</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>肉鹼穿梭</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>β-氧化</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>去胺作用</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>生糖胺基酸</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -806,30 +806,30 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>轉胺作用</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>氨</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>麩醯胺</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>尿素</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>轉胺作用</t>
-        </is>
-      </c>
       <c r="F11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -876,30 +876,30 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
+          <t>酮體</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>麩胺酸</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>銨離子</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>尿素</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>銨離子</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>麩胺酸</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>酮體</t>
-        </is>
-      </c>
       <c r="F13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -911,30 +911,30 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
+          <t>尿素循環</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>脂解作用</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>生酮作用</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>去胺作用</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>脂解作用</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>尿素循環</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>生酮作用</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>麩醯胺</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>生酮作用</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -981,30 +981,30 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
+          <t>β-氧化</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>銨離子</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>麩醯胺</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>轉胺酶</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>銨離子</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>β-氧化</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>麩醯胺</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1016,30 +1016,30 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
+          <t>去胺作用</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>生酮作用</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>醯基輔酶A</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>生酮胺基酸</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>生酮作用</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>去胺作用</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>醯基輔酶A</t>
-        </is>
-      </c>
       <c r="F17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1051,19 +1051,19 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
+          <t>生糖胺基酸</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>β-氧化</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>生酮胺基酸</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>β-氧化</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>生糖胺基酸</t>
-        </is>
-      </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
           <t>尿素循環</t>
@@ -1074,7 +1074,147 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>(標圖:w16_beta_ox_labeled) 標號1這一步驟的產物是什麼?</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>黃素腺嘌呤二核苷酸</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>輔酶A</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>菸鹼醯胺腺嘌呤二核苷酸</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>乙醯輔酶A</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>(標圖:w16_urea_labeled) 標號4這一步驟的最終產物是什麼?</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>鳥胺酸</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>尿素</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>精胺酸</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>瓜胺酸</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>哪一個配對正確?</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>尿素循環—完全發生於細胞質基質</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>麩胺酸—去胺作用釋放氨</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>生糖胺基酸—進入生酮路徑</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>肉鹼穿梭—用於脂肪酸合成反應</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>一分子C16棕櫚酸經β-氧化，共需幾輪、產生幾個乙醯輔酶A?</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>7輪，產生8個乙醯輔酶A</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>6輪，產生7個乙醯輔酶A</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>7輪，產生7個乙醯輔酶A</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>8輪，產生8個乙醯輔酶A</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
